--- a/data/bookings.xlsx
+++ b/data/bookings.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Bookings" sheetId="1" r:id="rId1"/>
   </sheets>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -714,9 +714,248 @@
         <v>11/10/2025, 4:56:20 pm</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>f9b0d3f9-fe6c-4f5e-a47e-27ea7d2f9c58</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Sailakhsmi</v>
+      </c>
+      <c r="C10" t="str">
+        <v>sailakshmisinghbaghel@gmail.com</v>
+      </c>
+      <c r="D10" t="str">
+        <v>09424309363</v>
+      </c>
+      <c r="E10" t="str">
+        <v>18/10/2025</v>
+      </c>
+      <c r="F10" t="str">
+        <v>12:30</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Hair Cut &amp; Styling, Hair Treatment &amp; Conditioning, Professional Blowdry &amp; Styling, Creative Braiding &amp; Fun Styles, Kids Haircuts &amp; Styling</v>
+      </c>
+      <c r="H10" t="str">
+        <v>Kadubeesanhalli, Sarjapur Road, Near Krishna Tech Park</v>
+      </c>
+      <c r="I10">
+        <v>1550</v>
+      </c>
+      <c r="J10" t="str">
+        <v>booking confirmed</v>
+      </c>
+      <c r="K10" t="str">
+        <v>14/10/2025, 11:03:38 am</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>BG20251014202110</v>
+      </c>
+      <c r="B11" t="str">
+        <v>My</v>
+      </c>
+      <c r="C11" t="str">
+        <v>+919876543210</v>
+      </c>
+      <c r="D11" t="str">
+        <v>haircut</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Wednesday, October 15</v>
+      </c>
+      <c r="F11" t="str">
+        <v>2 PM</v>
+      </c>
+      <c r="G11" t="str">
+        <v>123 Main Street</v>
+      </c>
+      <c r="H11" t="str">
+        <v>confirmed</v>
+      </c>
+      <c r="I11" t="str">
+        <v>2025-10-14T20:21:10.585199</v>
+      </c>
+      <c r="J11" t="str">
+        <v>voice_call</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>BG20251014202112</v>
+      </c>
+      <c r="B12" t="str">
+        <v>My</v>
+      </c>
+      <c r="C12" t="str">
+        <v>+919876543210</v>
+      </c>
+      <c r="D12" t="str">
+        <v>haircut</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Wednesday, October 15</v>
+      </c>
+      <c r="F12" t="str">
+        <v>10 AM</v>
+      </c>
+      <c r="G12" t="str">
+        <v>123 Main Street, Mumbai</v>
+      </c>
+      <c r="H12" t="str">
+        <v>confirmed</v>
+      </c>
+      <c r="I12" t="str">
+        <v>2025-10-14T20:21:12.225930</v>
+      </c>
+      <c r="J12" t="str">
+        <v>voice_call</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>5e7ad2a7-1488-4ef1-87bb-d48684ee432c</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Customer</v>
+      </c>
+      <c r="C13" t="str">
+        <v/>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v>19/10/2025</v>
+      </c>
+      <c r="F13" t="str">
+        <v>12:00 pm</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Hair Consultation &amp; Advice, Kids Hair Wash &amp; Conditioning</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13">
+        <v>250</v>
+      </c>
+      <c r="J13" t="str">
+        <v>booking confirmed</v>
+      </c>
+      <c r="K13" t="str">
+        <v>15/10/2025, 12:52:27 pm</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>9b962d49-78db-4e66-9fc8-85d548b778c5</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Sailakhsmi</v>
+      </c>
+      <c r="C14" t="str">
+        <v>sailakshmisinghbaghel@gmail.com</v>
+      </c>
+      <c r="D14" t="str">
+        <v>9424309363</v>
+      </c>
+      <c r="E14" t="str">
+        <v>21/10/2025</v>
+      </c>
+      <c r="F14" t="str">
+        <v>01:30 pm</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Hair Cut &amp; Styling, Bridal &amp; Party Hair Styling</v>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14">
+        <v>1200</v>
+      </c>
+      <c r="J14" t="str">
+        <v>confirmed booking</v>
+      </c>
+      <c r="K14" t="str">
+        <v>17/10/2025, 2:25:16 am</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>9942e120-9d17-475c-aa1f-99a03bff119a</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Sailakhsmi</v>
+      </c>
+      <c r="C15" t="str">
+        <v>sailakshmisinghbaghel@gmail.com</v>
+      </c>
+      <c r="D15" t="str">
+        <v>9424309363</v>
+      </c>
+      <c r="E15" t="str">
+        <v>21/10/2025</v>
+      </c>
+      <c r="F15" t="str">
+        <v>01:30 pm</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Hair Cut &amp; Styling, Bridal &amp; Party Hair Styling</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15">
+        <v>1200</v>
+      </c>
+      <c r="J15" t="str">
+        <v>confirmed booking</v>
+      </c>
+      <c r="K15" t="str">
+        <v>17/10/2025, 2:25:18 am</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>41ddfdff-4271-4adb-8b51-6078f14945d0</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Sailakhsmi</v>
+      </c>
+      <c r="C16" t="str">
+        <v>sailakshmisinghbaghel@gmail.com</v>
+      </c>
+      <c r="D16" t="str">
+        <v>9424309363</v>
+      </c>
+      <c r="E16" t="str">
+        <v>21/10/2025</v>
+      </c>
+      <c r="F16" t="str">
+        <v>01:30 pm</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Hair Cut &amp; Styling, Bridal &amp; Party Hair Styling</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16">
+        <v>1200</v>
+      </c>
+      <c r="J16" t="str">
+        <v>confirmed booking</v>
+      </c>
+      <c r="K16" t="str">
+        <v>17/10/2025, 2:25:20 am</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/bookings.xlsx
+++ b/data/bookings.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K26"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -953,9 +953,359 @@
         <v>17/10/2025, 2:25:20 am</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>c3c5e15e-2737-4c15-89c2-735569b34fcd</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Sailakhsmi</v>
+      </c>
+      <c r="C17" t="str">
+        <v>sailakshmisinghbaghel@gmail.com</v>
+      </c>
+      <c r="D17" t="str">
+        <v>9424309363</v>
+      </c>
+      <c r="E17" t="str">
+        <v>22/10/2025</v>
+      </c>
+      <c r="F17" t="str">
+        <v>12:00 pm</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Kids Hair Wash &amp; Conditioning, Hair Consultation &amp; Advice, Hair Coloring &amp; Highlights</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17">
+        <v>1450</v>
+      </c>
+      <c r="J17" t="str">
+        <v>booking</v>
+      </c>
+      <c r="K17" t="str">
+        <v>17/10/2025, 3:41:28 pm</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>f32a9d4c-b0d4-44cc-b190-dc3fd2299f05</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Sailakhsmi</v>
+      </c>
+      <c r="C18" t="str">
+        <v>sailakshmisinghbaghel@gmail.com</v>
+      </c>
+      <c r="D18" t="str">
+        <v>9424309363</v>
+      </c>
+      <c r="E18" t="str">
+        <v>22/10/2025</v>
+      </c>
+      <c r="F18" t="str">
+        <v>12:00 pm</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Kids Hair Wash &amp; Conditioning, Hair Consultation &amp; Advice, Hair Coloring &amp; Highlights</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18">
+        <v>1450</v>
+      </c>
+      <c r="J18" t="str">
+        <v>booking</v>
+      </c>
+      <c r="K18" t="str">
+        <v>17/10/2025, 3:41:30 pm</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>43361d12-cd7b-4027-8962-b700292d787b</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Sailakhsmi</v>
+      </c>
+      <c r="C19" t="str">
+        <v>sailakshmisinghbaghel@gmail.com</v>
+      </c>
+      <c r="D19" t="str">
+        <v>9424309363</v>
+      </c>
+      <c r="E19" t="str">
+        <v>22/10/2025</v>
+      </c>
+      <c r="F19" t="str">
+        <v>12:00 pm</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Kids Hair Wash &amp; Conditioning, Hair Consultation &amp; Advice, Hair Coloring &amp; Highlights</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19">
+        <v>1450</v>
+      </c>
+      <c r="J19" t="str">
+        <v>booking</v>
+      </c>
+      <c r="K19" t="str">
+        <v>17/10/2025, 3:41:32 pm</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>d618c21d-a70c-4e10-a228-25d6488613d5</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Sailakhsmi</v>
+      </c>
+      <c r="C20" t="str">
+        <v>sailakshmisinghbaghel@gmail.com</v>
+      </c>
+      <c r="D20" t="str">
+        <v>9424309363</v>
+      </c>
+      <c r="E20" t="str">
+        <v>22/10/2025</v>
+      </c>
+      <c r="F20" t="str">
+        <v>12:00 pm</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Kids Hair Wash &amp; Conditioning, Hair Consultation &amp; Advice, Hair Coloring &amp; Highlights</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20">
+        <v>1450</v>
+      </c>
+      <c r="J20" t="str">
+        <v>booking</v>
+      </c>
+      <c r="K20" t="str">
+        <v>17/10/2025, 3:41:34 pm</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>45f17d0e-3618-41e5-9534-3aa5418fc7d7</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Sailakhsmi</v>
+      </c>
+      <c r="C21" t="str">
+        <v>sailakshmi.baghel.aiml22@ggits.net</v>
+      </c>
+      <c r="D21" t="str">
+        <v>9424309363</v>
+      </c>
+      <c r="E21" t="str">
+        <v>22/10/2025</v>
+      </c>
+      <c r="F21" t="str">
+        <v>02:30 pm</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Hair Cut &amp; Styling, Hair Wash &amp; Basic Styling, Kids Haircuts &amp; Styling</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21">
+        <v>750</v>
+      </c>
+      <c r="J21" t="str">
+        <v>confimed booking</v>
+      </c>
+      <c r="K21" t="str">
+        <v>17/10/2025, 4:40:21 pm</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>35405fa0-9479-4ce7-9619-b53f51df2b98</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Chandhana</v>
+      </c>
+      <c r="C22" t="str">
+        <v>chandhanavv3@gmail.com</v>
+      </c>
+      <c r="D22" t="str">
+        <v>8147563261</v>
+      </c>
+      <c r="E22" t="str">
+        <v>27/10/2025</v>
+      </c>
+      <c r="F22" t="str">
+        <v>01:00 pm</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Hair Cut &amp; Styling, Bridal &amp; Party Hair Styling, Kids Haircuts &amp; Styling, Creative Braiding &amp; Fun Styles</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22">
+        <v>1500</v>
+      </c>
+      <c r="J22" t="str">
+        <v>booking done</v>
+      </c>
+      <c r="K22" t="str">
+        <v>22/10/2025, 1:49:58 pm</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>bf114740-fc57-4616-9d00-06534baf36d4</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Sailakshmi Singh Baghel</v>
+      </c>
+      <c r="C23" t="str">
+        <v>sailakshmisinghbaghel@gmail.com</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v>26/10/2025</v>
+      </c>
+      <c r="F23" t="str">
+        <v>01:30 pm</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Hair Treatment &amp; Conditioning, Creative Braiding &amp; Fun Styles</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23">
+        <v>750</v>
+      </c>
+      <c r="J23" t="str">
+        <v>confirmed booking</v>
+      </c>
+      <c r="K23" t="str">
+        <v>22/10/2025, 4:09:30 pm</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>d3aadab9-f9c1-44fb-97ab-ec16ee582c1e</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Sailakshmi Singh Baghel</v>
+      </c>
+      <c r="C24" t="str">
+        <v>sailakshmisinghbaghel@gmail.com</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v>26/10/2025</v>
+      </c>
+      <c r="F24" t="str">
+        <v>01:30 pm</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Hair Treatment &amp; Conditioning, Creative Braiding &amp; Fun Styles</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24">
+        <v>750</v>
+      </c>
+      <c r="J24" t="str">
+        <v>confirmed booking</v>
+      </c>
+      <c r="K24" t="str">
+        <v>22/10/2025, 4:09:40 pm</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>81737a35-53b5-4b2d-91ee-ffa3ca04259e</v>
+      </c>
+      <c r="B25" t="str">
+        <v>chandhana</v>
+      </c>
+      <c r="C25" t="str">
+        <v>chandhramana@gmail.com</v>
+      </c>
+      <c r="D25" t="str">
+        <v>8147563261</v>
+      </c>
+      <c r="E25" t="str">
+        <v>23/10/2025</v>
+      </c>
+      <c r="F25" t="str">
+        <v>09:00 am</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Hair Cut &amp; Styling, Hair Coloring &amp; Highlights, Hair Wash &amp; Basic Styling, Professional Blowdry &amp; Styling, Hair Treatment &amp; Conditioning</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25">
+        <v>2650</v>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v>22/10/2025, 4:21:57 pm</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>ef59b5eb-ecba-41b7-8f3b-aa8385387c59</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Sailakshmi Singh Baghel</v>
+      </c>
+      <c r="C26" t="str">
+        <v>sailakshmisinghbaghel@gmail.com</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v>26/10/2025</v>
+      </c>
+      <c r="F26" t="str">
+        <v>01:30 pm</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Hair Cut &amp; Styling, Bridal &amp; Party Hair Styling, Kids Haircuts &amp; Styling</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26">
+        <v>1350</v>
+      </c>
+      <c r="J26" t="str">
+        <v>booking confirmed</v>
+      </c>
+      <c r="K26" t="str">
+        <v>22/10/2025, 5:07:22 pm</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K26"/>
   </ignoredErrors>
 </worksheet>
 </file>